--- a/勤怠/勤怠_テスト次郎.xlsx
+++ b/勤怠/勤怠_テスト次郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\勤怠\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803A7995-4048-4841-9634-F18BDCB6E46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2775D9D2-AC55-4E4B-B3CA-87AF22644526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7800" yWindow="7800" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/勤怠/勤怠_テスト次郎.xlsx
+++ b/勤怠/勤怠_テスト次郎.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\masaki\Desktop\sample\勤怠\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2775D9D2-AC55-4E4B-B3CA-87AF22644526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B59D7D-C049-4F8A-9411-2F229BE45A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7800" yWindow="7800" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7020" yWindow="7020" windowWidth="43200" windowHeight="23445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
